--- a/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
+++ b/filesystem/Finance/Billing/Q4_2025_billing_export.xlsx
@@ -1944,10 +1944,10 @@
         <v>8470</v>
       </c>
       <c r="E33" s="36" t="n">
-        <v>11050</v>
+        <v>9350</v>
       </c>
       <c r="F33" s="37" t="n">
-        <v>27660</v>
+        <v>25960</v>
       </c>
       <c r="G33" s="38" t="n">
         <v>3</v>
@@ -2331,11 +2331,11 @@
       </c>
       <c r="E45" s="47">
         <f>SUM(E5:E44)</f>
-        <v>548184</v>
+        <v>546484</v>
       </c>
       <c r="F45" s="47">
         <f>SUM(F5:F44)</f>
-        <v>1593900</v>
+        <v>1592200</v>
       </c>
       <c r="G45" s="48">
         <f>SUM(G5:G44)</f>
